--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_325_R33.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_325_R33.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.8006</v>
+        <v>6.6309</v>
       </c>
       <c r="E2" t="n">
-        <v>3.4761</v>
+        <v>4.1719</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3245</v>
+        <v>2.4589</v>
       </c>
       <c r="G2" t="n">
         <v>2.51</v>
@@ -610,13 +610,13 @@
         <v>1.8556</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.4569</v>
+        <v>0.3734</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.187</v>
+        <v>-0.4911</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7301</v>
+        <v>0.8646</v>
       </c>
       <c r="V2" t="n">
         <v>1.8919</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.5345</v>
+        <v>5.6098</v>
       </c>
       <c r="E3" t="n">
-        <v>4.7897</v>
+        <v>5.1003</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7448</v>
+        <v>0.5095</v>
       </c>
       <c r="G3" t="n">
         <v>3.7076</v>
@@ -688,13 +688,13 @@
         <v>1.8556</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5074</v>
+        <v>0.5827</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.8804</v>
+        <v>-0.5698</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3878</v>
+        <v>1.1525</v>
       </c>
       <c r="V3" t="n">
         <v>-0.5361</v>
@@ -721,10 +721,10 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4437</v>
+        <v>2.3572</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2842</v>
+        <v>-0.3707</v>
       </c>
       <c r="F4" t="n">
         <v>2.7279</v>
@@ -766,10 +766,10 @@
         <v>1.8556</v>
       </c>
       <c r="S4" t="n">
-        <v>0.7625999999999999</v>
+        <v>0.6761</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1766</v>
+        <v>-0.2631</v>
       </c>
       <c r="U4" t="n">
         <v>0.9392</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.4355</v>
+        <v>2.0315</v>
       </c>
       <c r="E5" t="n">
-        <v>2.1254</v>
+        <v>1.8895</v>
       </c>
       <c r="F5" t="n">
-        <v>0.3101</v>
+        <v>0.142</v>
       </c>
       <c r="G5" t="n">
         <v>1.6944</v>
@@ -844,13 +844,13 @@
         <v>1.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5091</v>
+        <v>0.1052</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0272</v>
+        <v>-0.2631</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5364</v>
+        <v>0.3684</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.273</v>
+        <v>-0.2058</v>
       </c>
       <c r="E6" t="n">
         <v>-0.224</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.049</v>
+        <v>0.0183</v>
       </c>
       <c r="G6" t="n">
         <v>-0.4004</v>
@@ -922,13 +922,13 @@
         <v>0.4639</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3365</v>
+        <v>-0.2693</v>
       </c>
       <c r="T6" t="n">
         <v>-0.224</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1125</v>
+        <v>-0.0452</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. POKUSEVSKI</t>
+          <t>A. LAKIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9906</v>
+        <v>-1.1476</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.0452</v>
+        <v>-2.7625</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0546</v>
+        <v>1.6149</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.0275</v>
+        <v>-2.8414</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.4729</v>
+        <v>-0.2917</v>
       </c>
       <c r="I7" t="n">
-        <v>1.4454</v>
+        <v>-2.5497</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1649</v>
+        <v>-2.9843</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.7709</v>
+        <v>0.08749999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>1.606</v>
+        <v>-3.0718</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.8626</v>
+        <v>0.1428</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.7021</v>
+        <v>-0.3792</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1605</v>
+        <v>0.5221</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.1598</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>1.1598</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2482</v>
+        <v>-0.002</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2794</v>
+        <v>-0.3143</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0312</v>
+        <v>0.3123</v>
       </c>
       <c r="V7" t="n">
-        <v>0.7886</v>
+        <v>0.5361</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X7" t="n">
-        <v>0.7886</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. LAKIC</t>
+          <t>B. FERNANDO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1385</v>
+        <v>-1.1928</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.9551</v>
+        <v>-2.8928</v>
       </c>
       <c r="F8" t="n">
-        <v>1.8166</v>
+        <v>1.7</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.8414</v>
+        <v>-0.4512</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2917</v>
+        <v>-1.1104</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.5497</v>
+        <v>0.6592</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.9843</v>
+        <v>-0.3724</v>
       </c>
       <c r="K8" t="n">
-        <v>0.08749999999999999</v>
+        <v>-1.0349</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.0718</v>
+        <v>0.6625</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1428</v>
+        <v>-0.07870000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3792</v>
+        <v>-0.0755</v>
       </c>
       <c r="O8" t="n">
-        <v>0.5221</v>
+        <v>-0.0033</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1598</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="S8" t="n">
-        <v>0.007</v>
+        <v>-0.2418</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.507</v>
+        <v>-0.3969</v>
       </c>
       <c r="U8" t="n">
-        <v>0.514</v>
+        <v>0.1551</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5361</v>
+        <v>1.3558</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5361</v>
+        <v>1.3558</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B. FERNANDO</t>
+          <t>A. POKUSEVSKI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4676</v>
+        <v>-1.2869</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.2348</v>
+        <v>-1.4424</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7672</v>
+        <v>0.1554</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.4512</v>
+        <v>-2.0275</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.1104</v>
+        <v>-3.4729</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6592</v>
+        <v>1.4454</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3724</v>
+        <v>-0.1649</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.0349</v>
+        <v>-1.7709</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6625</v>
+        <v>1.606</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.07870000000000001</v>
+        <v>-1.8626</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0755</v>
+        <v>-1.7021</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0033</v>
+        <v>-0.1605</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.8556</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.5165999999999999</v>
+        <v>-0.0481</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7389</v>
+        <v>-0.1177</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2223</v>
+        <v>0.0696</v>
       </c>
       <c r="V9" t="n">
-        <v>1.3558</v>
+        <v>0.7886</v>
       </c>
       <c r="W9" t="n">
-        <v>1.3558</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.0926</v>
+        <v>-2.8664</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6843</v>
+        <v>-1.4917</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4083</v>
+        <v>-1.3747</v>
       </c>
       <c r="G10" t="n">
         <v>-2.9864</v>
@@ -1234,13 +1234,13 @@
         <v>1.6237</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6576</v>
+        <v>-0.4314</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5816</v>
+        <v>-0.389</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.076</v>
+        <v>-0.0424</v>
       </c>
       <c r="V10" t="n">
         <v>-1.0722</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.1688</v>
+        <v>-3.9192</v>
       </c>
       <c r="E11" t="n">
-        <v>-6.5068</v>
+        <v>-6.5934</v>
       </c>
       <c r="F11" t="n">
-        <v>2.3381</v>
+        <v>2.6741</v>
       </c>
       <c r="G11" t="n">
         <v>-0.1819</v>
@@ -1312,13 +1312,13 @@
         <v>1.8556</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2399</v>
+        <v>0.4894</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2513</v>
+        <v>-0.3378</v>
       </c>
       <c r="U11" t="n">
-        <v>0.4911</v>
+        <v>0.8272</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2836</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.758</v>
+        <v>-4.5654</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.3005</v>
+        <v>-4.1078</v>
       </c>
       <c r="F12" t="n">
         <v>-0.4576</v>
@@ -1390,10 +1390,10 @@
         <v>1.3917</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.68</v>
+        <v>-0.4874</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6563</v>
+        <v>-0.4637</v>
       </c>
       <c r="U12" t="n">
         <v>-0.0237</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3252000000000024</v>
+        <v>1.4453</v>
       </c>
       <c r="E13" t="n">
-        <v>-9.843699999999998</v>
+        <v>-8.723599999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>10.1689</v>
+        <v>10.1687</v>
       </c>
       <c r="G13" t="n">
         <v>-2.201100000000001</v>
@@ -1468,16 +1468,16 @@
         <v>16.2367</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.3734</v>
+        <v>0.7468000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.9509</v>
+        <v>-3.8305</v>
       </c>
       <c r="U13" t="n">
-        <v>4.577500000000001</v>
+        <v>4.5776</v>
       </c>
       <c r="V13" t="n">
-        <v>5.219199999999999</v>
+        <v>5.219200000000001</v>
       </c>
       <c r="W13" t="n">
         <v>7.8201</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.7393</v>
+        <v>2.9929</v>
       </c>
       <c r="E14" t="n">
-        <v>3.5114</v>
+        <v>2.6857</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2279</v>
+        <v>0.3072</v>
       </c>
       <c r="G14" t="n">
         <v>1.5795</v>
@@ -1546,13 +1546,13 @@
         <v>1.1598</v>
       </c>
       <c r="S14" t="n">
-        <v>2.0722</v>
+        <v>1.3258</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1325</v>
+        <v>0.3068</v>
       </c>
       <c r="U14" t="n">
-        <v>0.9397</v>
+        <v>1.019</v>
       </c>
       <c r="V14" t="n">
         <v>-1.0722</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.966</v>
+        <v>2.4372</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6215</v>
+        <v>1.3856</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3445</v>
+        <v>1.0516</v>
       </c>
       <c r="G15" t="n">
         <v>1.2472</v>
@@ -1624,13 +1624,13 @@
         <v>0.6959</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1647</v>
+        <v>0.6359</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2636</v>
+        <v>0.0277</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.0988</v>
+        <v>0.6082</v>
       </c>
       <c r="V15" t="n">
         <v>-0.1418</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Z. SELJAAS</t>
+          <t>T. HEURTEL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,58 +1657,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7444</v>
+        <v>1.2903</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.9755</v>
+        <v>-1.1446</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7199</v>
+        <v>2.4349</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.8344</v>
+        <v>5.9647</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4261</v>
+        <v>2.6289</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4082</v>
+        <v>3.3358</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.9166</v>
+        <v>6.4151</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.7191</v>
+        <v>2.4437</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.1975</v>
+        <v>3.9714</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0822</v>
+        <v>-0.4504</v>
       </c>
       <c r="N16" t="n">
-        <v>0.293</v>
+        <v>0.1852</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2108</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P16" t="n">
-        <v>1.1598</v>
+        <v>-4.871</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-6.9585</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1598</v>
+        <v>2.0876</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4191</v>
+        <v>0.1966</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0589</v>
+        <v>-0.6012</v>
       </c>
       <c r="U16" t="n">
-        <v>0.478</v>
+        <v>0.7978</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>T. HEURTEL</t>
+          <t>Z. SELJAAS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0614</v>
+        <v>0.6772</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.4984</v>
+        <v>-0.9755</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5598</v>
+        <v>1.6527</v>
       </c>
       <c r="G17" t="n">
-        <v>5.9647</v>
+        <v>-0.8344</v>
       </c>
       <c r="H17" t="n">
-        <v>2.6289</v>
+        <v>-0.4261</v>
       </c>
       <c r="I17" t="n">
-        <v>3.3358</v>
+        <v>-0.4082</v>
       </c>
       <c r="J17" t="n">
-        <v>6.4151</v>
+        <v>-0.9166</v>
       </c>
       <c r="K17" t="n">
-        <v>2.4437</v>
+        <v>-0.7191</v>
       </c>
       <c r="L17" t="n">
-        <v>3.9714</v>
+        <v>-0.1975</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4504</v>
+        <v>0.0822</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1852</v>
+        <v>0.293</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-0.2108</v>
       </c>
       <c r="P17" t="n">
-        <v>-4.871</v>
+        <v>1.1598</v>
       </c>
       <c r="Q17" t="n">
-        <v>-6.9585</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0876</v>
+        <v>1.1598</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.0324</v>
+        <v>0.3519</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.955</v>
+        <v>-0.0589</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.07729999999999999</v>
+        <v>0.4107</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>B. MASSA</t>
+          <t>M. NDIAYE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2254</v>
+        <v>-0.0741</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.4284</v>
+        <v>-2.94</v>
       </c>
       <c r="F18" t="n">
-        <v>1.203</v>
+        <v>2.8658</v>
       </c>
       <c r="G18" t="n">
-        <v>0.2172</v>
+        <v>1.4523</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9867</v>
+        <v>2.1548</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7695</v>
+        <v>-0.7026</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9678</v>
+        <v>1.4521</v>
       </c>
       <c r="K18" t="n">
-        <v>0.8942</v>
+        <v>1.4655</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0736</v>
+        <v>-0.0134</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7504999999999999</v>
+        <v>0.0002</v>
       </c>
       <c r="N18" t="n">
-        <v>0.0926</v>
+        <v>0.6893</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.8431</v>
+        <v>-0.6891</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9278</v>
+        <v>-2.3195</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1598</v>
+        <v>-4.639</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0876</v>
+        <v>2.3195</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0457</v>
+        <v>0.5406</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5895</v>
+        <v>-0.8252</v>
       </c>
       <c r="U18" t="n">
-        <v>0.5439000000000001</v>
+        <v>1.3658</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.3247</v>
+        <v>0.2525</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.6468</v>
+        <v>1.0722</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-0.8197</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. EBOUA</t>
+          <t>B. MASSA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.8585</v>
+        <v>-0.3763</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.264</v>
+        <v>-1.3104</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5945</v>
+        <v>0.9341</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.1291</v>
+        <v>0.2172</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.2051</v>
+        <v>0.9867</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.9239</v>
+        <v>-0.7695</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5279</v>
+        <v>0.9678</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1849</v>
+        <v>0.8942</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7127</v>
+        <v>0.0736</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6012</v>
+        <v>-0.7504999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.39</v>
+        <v>0.0926</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.2112</v>
+        <v>-0.8431</v>
       </c>
       <c r="P19" t="n">
-        <v>1.8556</v>
+        <v>0.9278</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8556</v>
+        <v>2.0876</v>
       </c>
       <c r="S19" t="n">
-        <v>0.4872</v>
+        <v>-0.1966</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1221</v>
+        <v>-0.4716</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3651</v>
+        <v>0.275</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0722</v>
+        <v>-1.3247</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1418</v>
+        <v>-0.6468</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.214</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9482</v>
+        <v>-0.7066</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4951</v>
+        <v>-1.3772</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5469000000000001</v>
+        <v>0.6705</v>
       </c>
       <c r="G20" t="n">
         <v>-0.6141</v>
@@ -2014,13 +2014,13 @@
         <v>1.6237</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4037</v>
+        <v>-0.1621</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8136</v>
+        <v>-0.6956</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4099</v>
+        <v>0.5335</v>
       </c>
       <c r="V20" t="n">
         <v>-0.3943</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0533</v>
+        <v>-0.7718</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2458</v>
+        <v>-2.0099</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1925</v>
+        <v>1.2382</v>
       </c>
       <c r="G21" t="n">
         <v>-1.2345</v>
@@ -2092,13 +2092,13 @@
         <v>2.3195</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5843</v>
+        <v>-0.3027</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.187</v>
+        <v>-0.9510999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6027</v>
+        <v>0.6484</v>
       </c>
       <c r="V21" t="n">
         <v>-0.3943</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. NDIAYE</t>
+          <t>E. JACKSON</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.1014</v>
+        <v>-0.7884</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.2938</v>
+        <v>-1.8665</v>
       </c>
       <c r="F22" t="n">
-        <v>2.1924</v>
+        <v>1.078</v>
       </c>
       <c r="G22" t="n">
-        <v>1.4523</v>
+        <v>-0.9388</v>
       </c>
       <c r="H22" t="n">
-        <v>2.1548</v>
+        <v>-0.39</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7026</v>
+        <v>-0.5488</v>
       </c>
       <c r="J22" t="n">
-        <v>1.4521</v>
+        <v>-0.585</v>
       </c>
       <c r="K22" t="n">
-        <v>1.4655</v>
+        <v>-0.6183</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.0134</v>
+        <v>0.0333</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0002</v>
+        <v>-0.3538</v>
       </c>
       <c r="N22" t="n">
-        <v>0.6893</v>
+        <v>0.2283</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6891</v>
+        <v>-0.5821</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.3195</v>
+        <v>0.232</v>
       </c>
       <c r="Q22" t="n">
-        <v>-4.639</v>
+        <v>-1.1598</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3195</v>
+        <v>1.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4867</v>
+        <v>0.9906</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1791</v>
+        <v>-0.1217</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6923</v>
+        <v>1.1123</v>
       </c>
       <c r="V22" t="n">
-        <v>0.2525</v>
+        <v>-1.0722</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.8197</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>E. JACKSON</t>
+          <t>D. LIGHTY</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.1816</v>
+        <v>-1.2153</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.1024</v>
+        <v>-1.8804</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9207</v>
+        <v>0.6651</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.9388</v>
+        <v>-2.5088</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.39</v>
+        <v>-0.2736</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.5488</v>
+        <v>-2.2352</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.585</v>
+        <v>-1.0433</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.6183</v>
+        <v>0.1379</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0333</v>
+        <v>-1.1813</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.3538</v>
+        <v>-1.4655</v>
       </c>
       <c r="N23" t="n">
-        <v>0.2283</v>
+        <v>-0.4116</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.5821</v>
+        <v>-1.0539</v>
       </c>
       <c r="P23" t="n">
-        <v>0.232</v>
+        <v>1.8556</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3917</v>
+        <v>1.8556</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5975</v>
+        <v>-0.5621</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3576</v>
+        <v>-0.8371</v>
       </c>
       <c r="U23" t="n">
-        <v>0.955</v>
+        <v>0.275</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>D. LIGHTY</t>
+          <t>P. EBOUA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,40 +2281,40 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.4677</v>
+        <v>-1.4311</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.9984</v>
+        <v>-0.7358</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5306999999999999</v>
+        <v>-0.6953</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.5088</v>
+        <v>-2.1291</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.2736</v>
+        <v>-0.2051</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.2352</v>
+        <v>-1.9239</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.0433</v>
+        <v>-0.5279</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1379</v>
+        <v>0.1849</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.1813</v>
+        <v>-0.7127</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.4655</v>
+        <v>-1.6012</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.4116</v>
+        <v>-0.39</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.0539</v>
+        <v>-1.2112</v>
       </c>
       <c r="P24" t="n">
         <v>1.8556</v>
@@ -2326,22 +2326,22 @@
         <v>1.8556</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8145</v>
+        <v>-0.0854</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.955</v>
+        <v>-0.3497</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1406</v>
+        <v>0.2642</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="25">
@@ -2359,31 +2359,31 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.325</v>
+        <v>2.034</v>
       </c>
       <c r="E25" t="n">
-        <v>-10.1689</v>
+        <v>-10.169</v>
       </c>
       <c r="F25" t="n">
-        <v>9.8438</v>
+        <v>12.2028</v>
       </c>
       <c r="G25" t="n">
-        <v>2.201200000000001</v>
+        <v>2.2012</v>
       </c>
       <c r="H25" t="n">
-        <v>8.240899999999998</v>
+        <v>8.2409</v>
       </c>
       <c r="I25" t="n">
         <v>-6.0396</v>
       </c>
       <c r="J25" t="n">
-        <v>8.044399999999998</v>
+        <v>8.0444</v>
       </c>
       <c r="K25" t="n">
-        <v>6.6904</v>
+        <v>6.690400000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>1.3542</v>
+        <v>1.354200000000001</v>
       </c>
       <c r="M25" t="n">
         <v>-5.8432</v>
@@ -2395,7 +2395,7 @@
         <v>-7.393599999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>2.319699999999998</v>
+        <v>2.319699999999999</v>
       </c>
       <c r="Q25" t="n">
         <v>-16.2367</v>
@@ -2404,16 +2404,16 @@
         <v>18.5563</v>
       </c>
       <c r="S25" t="n">
-        <v>0.3734</v>
+        <v>2.7325</v>
       </c>
       <c r="T25" t="n">
-        <v>-4.5775</v>
+        <v>-4.5776</v>
       </c>
       <c r="U25" t="n">
-        <v>4.951099999999999</v>
+        <v>7.309900000000001</v>
       </c>
       <c r="V25" t="n">
-        <v>-5.219199999999999</v>
+        <v>-5.219200000000001</v>
       </c>
       <c r="W25" t="n">
         <v>2.6009</v>
